--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_24.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,3575 +469,6465 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:30.425</t>
+          <t>2026-05-29 09:45:47.766</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509186113</v>
+        <v>1780022746648</v>
       </c>
       <c r="C2" t="n">
-        <v>87261</v>
+        <v>81840</v>
       </c>
       <c r="D2" t="n">
-        <v>19369.96</v>
+        <v>-191.39</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G2" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1117</v>
+      </c>
+      <c r="L2" t="n">
+        <v>112</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:30.699</t>
+          <t>2026-05-29 09:45:47.989</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509186314</v>
+        <v>1780022746848</v>
       </c>
       <c r="C3" t="n">
-        <v>87185</v>
+        <v>81683</v>
       </c>
       <c r="D3" t="n">
-        <v>18325.47</v>
+        <v>-338.82</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G3" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L3" t="n">
+        <v>122</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:30.701</t>
+          <t>2026-05-29 09:45:47.992</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509186515</v>
+        <v>1780022747048</v>
       </c>
       <c r="C4" t="n">
-        <v>87405</v>
+        <v>81694</v>
       </c>
       <c r="D4" t="n">
-        <v>17629.19</v>
+        <v>-310.88</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G4" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>942</v>
+      </c>
+      <c r="L4" t="n">
+        <v>119</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:30.713</t>
+          <t>2026-05-29 09:45:48.448</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509186716</v>
+        <v>1780022747248</v>
       </c>
       <c r="C5" t="n">
-        <v>86192</v>
+        <v>81609</v>
       </c>
       <c r="D5" t="n">
-        <v>15534.73</v>
+        <v>-380.33</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G5" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L5" t="n">
+        <v>120</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:31.275</t>
+          <t>2026-05-29 09:45:48.457</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509186918</v>
+        <v>1780022747448</v>
       </c>
       <c r="C6" t="n">
-        <v>86370</v>
+        <v>81844</v>
       </c>
       <c r="D6" t="n">
-        <v>14936</v>
+        <v>-126.32</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G6" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L6" t="n">
+        <v>121</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:31.529</t>
+          <t>2026-05-29 09:45:48.718</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509187119</v>
+        <v>1780022747667</v>
       </c>
       <c r="C7" t="n">
-        <v>86564</v>
+        <v>81765</v>
       </c>
       <c r="D7" t="n">
-        <v>14383.2</v>
+        <v>-199</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G7" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L7" t="n">
+        <v>116</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:31.555</t>
+          <t>2026-05-29 09:45:48.775</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509187320</v>
+        <v>1780022747867</v>
       </c>
       <c r="C8" t="n">
-        <v>86537</v>
+        <v>81079</v>
       </c>
       <c r="D8" t="n">
-        <v>13637.04</v>
+        <v>-875.05</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>684</v>
+        <v>2299</v>
       </c>
       <c r="G8" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>906</v>
+      </c>
+      <c r="L8" t="n">
+        <v>129</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:31.805</t>
+          <t>2026-05-29 09:45:49.245</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509187521</v>
+        <v>1780022748067</v>
       </c>
       <c r="C9" t="n">
-        <v>86209</v>
+        <v>81750</v>
       </c>
       <c r="D9" t="n">
-        <v>12627.18</v>
+        <v>-160.3</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>684</v>
+        <v>2018</v>
       </c>
       <c r="G9" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L9" t="n">
+        <v>119</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:31.813</t>
+          <t>2026-05-29 09:45:49.247</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509187723</v>
+        <v>1780022748267</v>
       </c>
       <c r="C10" t="n">
-        <v>86215</v>
+        <v>80267</v>
       </c>
       <c r="D10" t="n">
-        <v>12001.83</v>
+        <v>-1635.28</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>684</v>
+        <v>2018</v>
       </c>
       <c r="G10" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>978</v>
+      </c>
+      <c r="L10" t="n">
+        <v>115</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:32.088</t>
+          <t>2026-05-29 09:45:49.707</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509187924</v>
+        <v>1780022748467</v>
       </c>
       <c r="C11" t="n">
-        <v>86076</v>
+        <v>79997</v>
       </c>
       <c r="D11" t="n">
-        <v>11262.73</v>
+        <v>-1823.52</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>684</v>
+        <v>2018</v>
       </c>
       <c r="G11" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1239</v>
+      </c>
+      <c r="L11" t="n">
+        <v>119</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.622</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:32.091</t>
+          <t>2026-05-29 09:45:49.708</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509188125</v>
+        <v>1780022748667</v>
       </c>
       <c r="C12" t="n">
-        <v>85666</v>
+        <v>80137</v>
       </c>
       <c r="D12" t="n">
-        <v>10289.6</v>
+        <v>-1592.34</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>684</v>
+        <v>2018</v>
       </c>
       <c r="G12" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L12" t="n">
+        <v>127</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:32.482</t>
+          <t>2026-05-29 09:45:49.936</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509188327</v>
+        <v>1780022748868</v>
       </c>
       <c r="C13" t="n">
-        <v>86464</v>
+        <v>80669</v>
       </c>
       <c r="D13" t="n">
-        <v>10573.12</v>
+        <v>-980.73</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>684</v>
+        <v>2018</v>
       </c>
       <c r="G13" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L13" t="n">
+        <v>106</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:32.792</t>
+          <t>2026-05-29 09:45:50.039</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509188528</v>
+        <v>1780022749067</v>
       </c>
       <c r="C14" t="n">
-        <v>87989</v>
+        <v>82090</v>
       </c>
       <c r="D14" t="n">
-        <v>11569.46</v>
+        <v>489.31</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G14" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>971</v>
+      </c>
+      <c r="L14" t="n">
+        <v>108</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.026</t>
+          <t>2026-05-29 09:45:50.388</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509188729</v>
+        <v>1780022749286</v>
       </c>
       <c r="C15" t="n">
-        <v>88214</v>
+        <v>82465</v>
       </c>
       <c r="D15" t="n">
-        <v>11215.99</v>
+        <v>839.84</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G15" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1101</v>
+      </c>
+      <c r="L15" t="n">
+        <v>116</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.027</t>
+          <t>2026-05-29 09:45:50.390</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509188930</v>
+        <v>1780022749486</v>
       </c>
       <c r="C16" t="n">
-        <v>88196</v>
+        <v>82756</v>
       </c>
       <c r="D16" t="n">
-        <v>10637.19</v>
+        <v>1088.85</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G16" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>903</v>
+      </c>
+      <c r="L16" t="n">
+        <v>118</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.071</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.443</t>
+          <t>2026-05-29 09:45:50.782</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509189132</v>
+        <v>1780022749687</v>
       </c>
       <c r="C17" t="n">
-        <v>88371</v>
+        <v>82569</v>
       </c>
       <c r="D17" t="n">
-        <v>10280.33</v>
+        <v>847.41</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G17" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L17" t="n">
+        <v>106</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.922</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.692</t>
+          <t>2026-05-29 09:45:50.805</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509189333</v>
+        <v>1780022749886</v>
       </c>
       <c r="C18" t="n">
-        <v>87588</v>
+        <v>81781</v>
       </c>
       <c r="D18" t="n">
-        <v>8983.309999999999</v>
+        <v>17.04</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G18" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>918</v>
+      </c>
+      <c r="L18" t="n">
+        <v>108</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.722</t>
+          <t>2026-05-29 09:45:51.531</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509189534</v>
+        <v>1780022750087</v>
       </c>
       <c r="C19" t="n">
-        <v>85872</v>
+        <v>82569</v>
       </c>
       <c r="D19" t="n">
-        <v>6818.15</v>
+        <v>804.1900000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G19" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L19" t="n">
+        <v>105</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.284</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.987</t>
+          <t>2026-05-29 09:45:51.533</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509189736</v>
+        <v>1780022750306</v>
       </c>
       <c r="C20" t="n">
-        <v>86078</v>
+        <v>81648</v>
       </c>
       <c r="D20" t="n">
-        <v>6683.24</v>
+        <v>-157.02</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G20" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1226</v>
+      </c>
+      <c r="L20" t="n">
+        <v>124</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:33.991</t>
+          <t>2026-05-29 09:45:51.612</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509189937</v>
+        <v>1780022750507</v>
       </c>
       <c r="C21" t="n">
-        <v>85424</v>
+        <v>82033</v>
       </c>
       <c r="D21" t="n">
-        <v>5695.08</v>
+        <v>235.83</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G21" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1104</v>
+      </c>
+      <c r="L21" t="n">
+        <v>106</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:34.255</t>
+          <t>2026-05-29 09:45:51.613</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509190138</v>
+        <v>1780022750706</v>
       </c>
       <c r="C22" t="n">
-        <v>83789</v>
+        <v>80605</v>
       </c>
       <c r="D22" t="n">
-        <v>3775.32</v>
+        <v>-1203.96</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G22" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>907</v>
+      </c>
+      <c r="L22" t="n">
+        <v>114</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:34.258</t>
+          <t>2026-05-29 09:45:51.926</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509190339</v>
+        <v>1780022750907</v>
       </c>
       <c r="C23" t="n">
-        <v>84589</v>
+        <v>81700</v>
       </c>
       <c r="D23" t="n">
-        <v>4386.56</v>
+        <v>-48.76</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G23" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1018</v>
+      </c>
+      <c r="L23" t="n">
+        <v>106</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.304</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.053</t>
+          <t>2026-05-29 09:45:51.937</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509190541</v>
+        <v>1780022751125</v>
       </c>
       <c r="C24" t="n">
-        <v>84402</v>
+        <v>80666</v>
       </c>
       <c r="D24" t="n">
-        <v>3980.23</v>
+        <v>-1080.33</v>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G24" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K24" t="n">
+        <v>811</v>
+      </c>
+      <c r="L24" t="n">
+        <v>120</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.732</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.350</t>
+          <t>2026-05-29 09:45:52.232</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509190742</v>
+        <v>1780022751325</v>
       </c>
       <c r="C25" t="n">
-        <v>84228</v>
+        <v>81273</v>
       </c>
       <c r="D25" t="n">
-        <v>3607.22</v>
+        <v>-419.31</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>2516</v>
+        <v>2018</v>
       </c>
       <c r="G25" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K25" t="n">
+        <v>906</v>
+      </c>
+      <c r="L25" t="n">
+        <v>120</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.352</t>
+          <t>2026-05-29 09:45:52.812</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509190943</v>
+        <v>1780022751526</v>
       </c>
       <c r="C26" t="n">
-        <v>84597</v>
+        <v>81826</v>
       </c>
       <c r="D26" t="n">
-        <v>3795.86</v>
+        <v>154.66</v>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F26" t="n">
-        <v>2516</v>
+        <v>3638</v>
       </c>
       <c r="G26" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1285</v>
+      </c>
+      <c r="L26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.353</t>
+          <t>2026-05-29 09:45:52.813</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509191145</v>
+        <v>1780022751725</v>
       </c>
       <c r="C27" t="n">
-        <v>86207</v>
+        <v>81769</v>
       </c>
       <c r="D27" t="n">
-        <v>5216.06</v>
+        <v>89.92</v>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F27" t="n">
-        <v>2516</v>
+        <v>3638</v>
       </c>
       <c r="G27" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1087</v>
+      </c>
+      <c r="L27" t="n">
+        <v>114</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.528</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.654</t>
+          <t>2026-05-29 09:45:52.866</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509191346</v>
+        <v>1780022751926</v>
       </c>
       <c r="C28" t="n">
-        <v>86266</v>
+        <v>81499</v>
       </c>
       <c r="D28" t="n">
-        <v>5014.26</v>
+        <v>-184.57</v>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F28" t="n">
-        <v>2516</v>
+        <v>3638</v>
       </c>
       <c r="G28" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K28" t="n">
+        <v>939</v>
+      </c>
+      <c r="L28" t="n">
+        <v>104</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.752</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.927</t>
+          <t>2026-05-29 09:45:53.021</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509191547</v>
+        <v>1780022752125</v>
       </c>
       <c r="C29" t="n">
-        <v>85150</v>
+        <v>81719</v>
       </c>
       <c r="D29" t="n">
-        <v>3647.55</v>
+        <v>44.66</v>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F29" t="n">
-        <v>2516</v>
+        <v>3638</v>
       </c>
       <c r="G29" t="n">
-        <v>313.92</v>
+        <v>300.24</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>894</v>
+      </c>
+      <c r="L29" t="n">
+        <v>108</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.266</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:35.928</t>
+          <t>2026-05-29 09:45:53.026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509191748</v>
+        <v>1780022752326</v>
       </c>
       <c r="C30" t="n">
-        <v>85962</v>
+        <v>82011</v>
       </c>
       <c r="D30" t="n">
-        <v>4277.17</v>
+        <v>334.42</v>
       </c>
       <c r="E30" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F30" t="n">
-        <v>2516</v>
+        <v>740</v>
       </c>
       <c r="G30" t="n">
-        <v>313.92</v>
+        <v>287.66</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K30" t="n">
+        <v>699</v>
+      </c>
+      <c r="L30" t="n">
+        <v>104</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:36.264</t>
+          <t>2026-05-29 09:45:53.530</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509191950</v>
+        <v>1780022752525</v>
       </c>
       <c r="C31" t="n">
-        <v>86431</v>
+        <v>82044</v>
       </c>
       <c r="D31" t="n">
-        <v>4532.31</v>
+        <v>350.7</v>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F31" t="n">
-        <v>2516</v>
+        <v>740</v>
       </c>
       <c r="G31" t="n">
-        <v>313.92</v>
+        <v>287.66</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L31" t="n">
+        <v>113</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.426</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:36.266</t>
+          <t>2026-05-29 09:45:54.074</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779509192151</v>
+        <v>1780022752745</v>
       </c>
       <c r="C32" t="n">
-        <v>86977</v>
+        <v>82271</v>
       </c>
       <c r="D32" t="n">
-        <v>4851.7</v>
+        <v>560.17</v>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F32" t="n">
-        <v>2516</v>
+        <v>740</v>
       </c>
       <c r="G32" t="n">
-        <v>313.92</v>
+        <v>287.66</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="J32" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1327</v>
+      </c>
+      <c r="L32" t="n">
+        <v>158</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.275</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:36.485</t>
+          <t>2026-05-29 09:45:54.075</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779509192352</v>
+        <v>1780022752944</v>
       </c>
       <c r="C33" t="n">
-        <v>87170</v>
+        <v>81137</v>
       </c>
       <c r="D33" t="n">
-        <v>4802.11</v>
+        <v>-601.84</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F33" t="n">
-        <v>2516</v>
+        <v>740</v>
       </c>
       <c r="G33" t="n">
-        <v>313.92</v>
+        <v>287.66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L33" t="n">
+        <v>137</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.842</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:36.764</t>
+          <t>2026-05-29 09:45:54.076</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779509192553</v>
+        <v>1780022753144</v>
       </c>
       <c r="C34" t="n">
-        <v>87371</v>
+        <v>82527</v>
       </c>
       <c r="D34" t="n">
-        <v>4763.01</v>
+        <v>818.25</v>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F34" t="n">
-        <v>2516</v>
+        <v>740</v>
       </c>
       <c r="G34" t="n">
-        <v>313.92</v>
+        <v>287.66</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K34" t="n">
+        <v>931</v>
+      </c>
+      <c r="L34" t="n">
+        <v>103</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.723</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.383</t>
+          <t>2026-05-29 09:45:54.336</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779509192755</v>
+        <v>1780022753344</v>
       </c>
       <c r="C35" t="n">
-        <v>87063</v>
+        <v>80877</v>
       </c>
       <c r="D35" t="n">
-        <v>4216.86</v>
+        <v>-872.66</v>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F35" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G35" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>991</v>
+      </c>
+      <c r="L35" t="n">
+        <v>118</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.662</t>
+          <t>2026-05-29 09:45:54.348</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779509192956</v>
+        <v>1780022753544</v>
       </c>
       <c r="C36" t="n">
-        <v>87109</v>
+        <v>78532</v>
       </c>
       <c r="D36" t="n">
-        <v>4052.01</v>
+        <v>-3174.03</v>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F36" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G36" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>803</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.663</t>
+          <t>2026-05-29 09:45:54.968</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779509193157</v>
+        <v>1780022753744</v>
       </c>
       <c r="C37" t="n">
-        <v>87388</v>
+        <v>75332</v>
       </c>
       <c r="D37" t="n">
-        <v>4128.41</v>
+        <v>-6215.33</v>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F37" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G37" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1223</v>
+      </c>
+      <c r="L37" t="n">
+        <v>126</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.066</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.664</t>
+          <t>2026-05-29 09:45:54.978</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779509193359</v>
+        <v>1780022753944</v>
       </c>
       <c r="C38" t="n">
-        <v>87268</v>
+        <v>76550</v>
       </c>
       <c r="D38" t="n">
-        <v>3801.99</v>
+        <v>-4686.56</v>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F38" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G38" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L38" t="n">
+        <v>106</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.926</t>
+          <t>2026-05-29 09:45:55.493</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779509193560</v>
+        <v>1780022754144</v>
       </c>
       <c r="C39" t="n">
-        <v>87213</v>
+        <v>77695</v>
       </c>
       <c r="D39" t="n">
-        <v>3556.89</v>
+        <v>-3307.23</v>
       </c>
       <c r="E39" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F39" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G39" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1348</v>
+      </c>
+      <c r="L39" t="n">
+        <v>119</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.657</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.928</t>
+          <t>2026-05-29 09:45:55.495</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779509193761</v>
+        <v>1780022754344</v>
       </c>
       <c r="C40" t="n">
-        <v>87410</v>
+        <v>78299</v>
       </c>
       <c r="D40" t="n">
-        <v>3576.05</v>
+        <v>-2537.87</v>
       </c>
       <c r="E40" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F40" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G40" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L40" t="n">
+        <v>104</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.795</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:37.929</t>
+          <t>2026-05-29 09:45:55.497</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779509193962</v>
+        <v>1780022754563</v>
       </c>
       <c r="C41" t="n">
-        <v>87098</v>
+        <v>80958</v>
       </c>
       <c r="D41" t="n">
-        <v>3085.25</v>
+        <v>248.02</v>
       </c>
       <c r="E41" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F41" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G41" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>932</v>
+      </c>
+      <c r="L41" t="n">
+        <v>112</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.597</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:38.554</t>
+          <t>2026-05-29 09:45:55.806</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779509194164</v>
+        <v>1780022754763</v>
       </c>
       <c r="C42" t="n">
-        <v>87234</v>
+        <v>81227</v>
       </c>
       <c r="D42" t="n">
-        <v>3066.98</v>
+        <v>504.62</v>
       </c>
       <c r="E42" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F42" t="n">
-        <v>2516</v>
+        <v>1019</v>
       </c>
       <c r="G42" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L42" t="n">
+        <v>120</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:38.777</t>
+          <t>2026-05-29 09:45:55.814</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779509194365</v>
+        <v>1780022754963</v>
       </c>
       <c r="C43" t="n">
-        <v>87446</v>
+        <v>79169</v>
       </c>
       <c r="D43" t="n">
-        <v>3125.63</v>
+        <v>-1578.61</v>
       </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F43" t="n">
-        <v>5898</v>
+        <v>1019</v>
       </c>
       <c r="G43" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>850</v>
+      </c>
+      <c r="L43" t="n">
+        <v>105</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:38.778</t>
+          <t>2026-05-29 09:45:56.098</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779509194566</v>
+        <v>1780022755163</v>
       </c>
       <c r="C44" t="n">
-        <v>87053</v>
+        <v>80735</v>
       </c>
       <c r="D44" t="n">
-        <v>2576.35</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F44" t="n">
-        <v>5898</v>
+        <v>1019</v>
       </c>
       <c r="G44" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K44" t="n">
+        <v>935</v>
+      </c>
+      <c r="L44" t="n">
+        <v>122</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.585</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.049</t>
+          <t>2026-05-29 09:45:56.099</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779509194768</v>
+        <v>1780022755363</v>
       </c>
       <c r="C45" t="n">
-        <v>87196</v>
+        <v>84053</v>
       </c>
       <c r="D45" t="n">
-        <v>2590.53</v>
+        <v>3381</v>
       </c>
       <c r="E45" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F45" t="n">
-        <v>5898</v>
+        <v>1019</v>
       </c>
       <c r="G45" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>735</v>
+      </c>
+      <c r="L45" t="n">
+        <v>106</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.736</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.050</t>
+          <t>2026-05-29 09:45:57.096</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779509194969</v>
+        <v>1780022755563</v>
       </c>
       <c r="C46" t="n">
-        <v>87367</v>
+        <v>82528</v>
       </c>
       <c r="D46" t="n">
-        <v>2632.01</v>
+        <v>1686.95</v>
       </c>
       <c r="E46" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F46" t="n">
-        <v>5898</v>
+        <v>1019</v>
       </c>
       <c r="G46" t="n">
-        <v>313.92</v>
+        <v>264.76</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1532</v>
+      </c>
+      <c r="L46" t="n">
+        <v>118</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.352</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.489</t>
+          <t>2026-05-29 09:45:57.097</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779509195170</v>
+        <v>1780022755763</v>
       </c>
       <c r="C47" t="n">
-        <v>86988</v>
+        <v>84869</v>
       </c>
       <c r="D47" t="n">
-        <v>2121.41</v>
+        <v>3943.61</v>
       </c>
       <c r="E47" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F47" t="n">
-        <v>664</v>
+        <v>1019</v>
       </c>
       <c r="G47" t="n">
-        <v>318.9</v>
+        <v>264.76</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1333</v>
+      </c>
+      <c r="L47" t="n">
+        <v>108</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.844</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.799</t>
+          <t>2026-05-29 09:45:57.099</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779509195371</v>
+        <v>1780022755963</v>
       </c>
       <c r="C48" t="n">
-        <v>87083</v>
+        <v>84741</v>
       </c>
       <c r="D48" t="n">
-        <v>2110.34</v>
+        <v>3618.43</v>
       </c>
       <c r="E48" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>664</v>
+        <v>1019</v>
       </c>
       <c r="G48" t="n">
-        <v>318.9</v>
+        <v>264.76</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L48" t="n">
+        <v>113</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.800</t>
+          <t>2026-05-29 09:45:57.100</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779509195573</v>
+        <v>1780022756163</v>
       </c>
       <c r="C49" t="n">
-        <v>87244</v>
+        <v>83538</v>
       </c>
       <c r="D49" t="n">
-        <v>2165.82</v>
+        <v>2234.5</v>
       </c>
       <c r="E49" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>664</v>
+        <v>1019</v>
       </c>
       <c r="G49" t="n">
-        <v>318.9</v>
+        <v>264.76</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>936</v>
+      </c>
+      <c r="L49" t="n">
+        <v>107</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.977</t>
+          <t>2026-05-29 09:45:57.453</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779509195774</v>
+        <v>1780022756382</v>
       </c>
       <c r="C50" t="n">
-        <v>87014</v>
+        <v>83213</v>
       </c>
       <c r="D50" t="n">
-        <v>1827.53</v>
+        <v>1797.78</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F50" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G50" t="n">
-        <v>313.42</v>
+        <v>264.76</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L50" t="n">
+        <v>123</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:39.978</t>
+          <t>2026-05-29 09:45:57.454</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779509195975</v>
+        <v>1780022756582</v>
       </c>
       <c r="C51" t="n">
-        <v>87112</v>
+        <v>83015</v>
       </c>
       <c r="D51" t="n">
-        <v>1834.15</v>
+        <v>1509.89</v>
       </c>
       <c r="E51" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F51" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G51" t="n">
-        <v>313.42</v>
+        <v>264.76</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>871</v>
+      </c>
+      <c r="L51" t="n">
+        <v>116</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.761</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:40.448</t>
+          <t>2026-05-29 09:45:57.973</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779509196177</v>
+        <v>1780022756782</v>
       </c>
       <c r="C52" t="n">
-        <v>87294</v>
+        <v>83619</v>
       </c>
       <c r="D52" t="n">
-        <v>1924.45</v>
+        <v>2038.4</v>
       </c>
       <c r="E52" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G52" t="n">
-        <v>313.42</v>
+        <v>264.76</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L52" t="n">
+        <v>122</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.573</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:40.682</t>
+          <t>2026-05-29 09:45:57.983</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779509196378</v>
+        <v>1780022756982</v>
       </c>
       <c r="C53" t="n">
-        <v>87111</v>
+        <v>83779</v>
       </c>
       <c r="D53" t="n">
-        <v>1645.22</v>
+        <v>2096.48</v>
       </c>
       <c r="E53" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F53" t="n">
-        <v>564</v>
+        <v>1019</v>
       </c>
       <c r="G53" t="n">
-        <v>314.45</v>
+        <v>264.76</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L53" t="n">
+        <v>110</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.957</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:40.939</t>
+          <t>2026-05-29 09:45:58.396</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779509196579</v>
+        <v>1780022757182</v>
       </c>
       <c r="C54" t="n">
-        <v>87304</v>
+        <v>83362</v>
       </c>
       <c r="D54" t="n">
-        <v>1755.96</v>
+        <v>1574.65</v>
       </c>
       <c r="E54" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F54" t="n">
-        <v>564</v>
+        <v>1019</v>
       </c>
       <c r="G54" t="n">
-        <v>314.45</v>
+        <v>264.76</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L54" t="n">
+        <v>119</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.003</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:40.939</t>
+          <t>2026-05-29 09:45:58.409</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779509196780</v>
+        <v>1780022757382</v>
       </c>
       <c r="C55" t="n">
-        <v>87457</v>
+        <v>83043</v>
       </c>
       <c r="D55" t="n">
-        <v>1821.16</v>
+        <v>1176.92</v>
       </c>
       <c r="E55" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>543</v>
+        <v>1019</v>
       </c>
       <c r="G55" t="n">
-        <v>311.94</v>
+        <v>264.76</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1026</v>
+      </c>
+      <c r="L55" t="n">
+        <v>107</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.029</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:40.940</t>
+          <t>2026-05-29 09:45:58.555</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779509196982</v>
+        <v>1780022757582</v>
       </c>
       <c r="C56" t="n">
-        <v>87527</v>
+        <v>82715</v>
       </c>
       <c r="D56" t="n">
-        <v>1800.11</v>
+        <v>790.0700000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F56" t="n">
-        <v>543</v>
+        <v>1019</v>
       </c>
       <c r="G56" t="n">
-        <v>311.94</v>
+        <v>264.76</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>971</v>
+      </c>
+      <c r="L56" t="n">
+        <v>116</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.967</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:41.281</t>
+          <t>2026-05-29 09:45:58.557</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779509197183</v>
+        <v>1780022757782</v>
       </c>
       <c r="C57" t="n">
-        <v>87064</v>
+        <v>82351</v>
       </c>
       <c r="D57" t="n">
-        <v>1247.1</v>
+        <v>386.57</v>
       </c>
       <c r="E57" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
-        <v>543</v>
+        <v>1019</v>
       </c>
       <c r="G57" t="n">
-        <v>311.94</v>
+        <v>264.76</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>774</v>
+      </c>
+      <c r="L57" t="n">
+        <v>113</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.381</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:41.547</t>
+          <t>2026-05-29 09:45:59.466</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779509197384</v>
+        <v>1780022757982</v>
       </c>
       <c r="C58" t="n">
-        <v>87210</v>
+        <v>82192</v>
       </c>
       <c r="D58" t="n">
-        <v>1330.75</v>
+        <v>208.24</v>
       </c>
       <c r="E58" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F58" t="n">
-        <v>543</v>
+        <v>1019</v>
       </c>
       <c r="G58" t="n">
-        <v>311.94</v>
+        <v>264.76</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1482</v>
+      </c>
+      <c r="L58" t="n">
+        <v>124</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.628</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:41.903</t>
+          <t>2026-05-29 09:45:59.468</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779509197586</v>
+        <v>1780022758201</v>
       </c>
       <c r="C59" t="n">
-        <v>87360</v>
+        <v>82037</v>
       </c>
       <c r="D59" t="n">
-        <v>1414.21</v>
+        <v>42.83</v>
       </c>
       <c r="E59" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F59" t="n">
-        <v>543</v>
+        <v>1019</v>
       </c>
       <c r="G59" t="n">
-        <v>311.94</v>
+        <v>264.76</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1266</v>
+      </c>
+      <c r="L59" t="n">
+        <v>108</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.726</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:42.198</t>
+          <t>2026-05-29 09:45:59.470</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779509197787</v>
+        <v>1780022758401</v>
       </c>
       <c r="C60" t="n">
-        <v>86815</v>
+        <v>81935</v>
       </c>
       <c r="D60" t="n">
-        <v>798.5</v>
+        <v>-61.31</v>
       </c>
       <c r="E60" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F60" t="n">
-        <v>886</v>
+        <v>1019</v>
       </c>
       <c r="G60" t="n">
-        <v>292.61</v>
+        <v>264.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L60" t="n">
+        <v>113</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.769</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:42.205</t>
+          <t>2026-05-29 09:45:59.471</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779509197988</v>
+        <v>1780022758601</v>
       </c>
       <c r="C61" t="n">
-        <v>87185</v>
+        <v>81636</v>
       </c>
       <c r="D61" t="n">
-        <v>1128.57</v>
+        <v>-357.25</v>
       </c>
       <c r="E61" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F61" t="n">
-        <v>886</v>
+        <v>1019</v>
       </c>
       <c r="G61" t="n">
-        <v>292.61</v>
+        <v>264.76</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>869</v>
+      </c>
+      <c r="L61" t="n">
+        <v>110</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.062</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:42.463</t>
+          <t>2026-05-29 09:45:59.736</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779509198190</v>
+        <v>1780022758801</v>
       </c>
       <c r="C62" t="n">
-        <v>87503</v>
+        <v>81664</v>
       </c>
       <c r="D62" t="n">
-        <v>1390.14</v>
+        <v>-311.38</v>
       </c>
       <c r="E62" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F62" t="n">
-        <v>886</v>
+        <v>1019</v>
       </c>
       <c r="G62" t="n">
-        <v>292.61</v>
+        <v>264.76</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K62" t="n">
+        <v>933</v>
+      </c>
+      <c r="L62" t="n">
+        <v>119</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.453</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:42.479</t>
+          <t>2026-05-29 09:46:00.043</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779509198391</v>
+        <v>1780022759002</v>
       </c>
       <c r="C63" t="n">
-        <v>87622</v>
+        <v>81707</v>
       </c>
       <c r="D63" t="n">
-        <v>1439.64</v>
+        <v>-252.81</v>
       </c>
       <c r="E63" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F63" t="n">
-        <v>564</v>
+        <v>1019</v>
       </c>
       <c r="G63" t="n">
-        <v>288.19</v>
+        <v>264.76</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1039</v>
+      </c>
+      <c r="L63" t="n">
+        <v>118</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.272</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:42.841</t>
+          <t>2026-05-29 09:46:00.044</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779509198592</v>
+        <v>1780022759201</v>
       </c>
       <c r="C64" t="n">
-        <v>87219</v>
+        <v>81514</v>
       </c>
       <c r="D64" t="n">
-        <v>964.66</v>
+        <v>-433.17</v>
       </c>
       <c r="E64" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F64" t="n">
-        <v>564</v>
+        <v>1019</v>
       </c>
       <c r="G64" t="n">
-        <v>288.19</v>
+        <v>264.76</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>842</v>
+      </c>
+      <c r="L64" t="n">
+        <v>118</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.168</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.204</t>
+          <t>2026-05-29 09:46:01.236</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779509198793</v>
+        <v>1780022759401</v>
       </c>
       <c r="C65" t="n">
-        <v>87600</v>
+        <v>81321</v>
       </c>
       <c r="D65" t="n">
-        <v>1297.42</v>
+        <v>-604.52</v>
       </c>
       <c r="E65" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F65" t="n">
-        <v>564</v>
+        <v>1019</v>
       </c>
       <c r="G65" t="n">
-        <v>288.19</v>
+        <v>264.76</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1833</v>
+      </c>
+      <c r="L65" t="n">
+        <v>122</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.553</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.371</t>
+          <t>2026-05-29 09:46:01.250</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779509198995</v>
+        <v>1780022759601</v>
       </c>
       <c r="C66" t="n">
-        <v>87670</v>
+        <v>81465</v>
       </c>
       <c r="D66" t="n">
-        <v>1302.55</v>
+        <v>-430.29</v>
       </c>
       <c r="E66" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F66" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G66" t="n">
-        <v>270.09</v>
+        <v>264.76</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L66" t="n">
+        <v>117</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.389</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.372</t>
+          <t>2026-05-29 09:46:01.361</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779509199196</v>
+        <v>1780022759801</v>
       </c>
       <c r="C67" t="n">
-        <v>87339</v>
+        <v>81478</v>
       </c>
       <c r="D67" t="n">
-        <v>906.42</v>
+        <v>-395.78</v>
       </c>
       <c r="E67" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F67" t="n">
-        <v>644</v>
+        <v>1019</v>
       </c>
       <c r="G67" t="n">
-        <v>270.09</v>
+        <v>264.76</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1559</v>
+      </c>
+      <c r="L67" t="n">
+        <v>122</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.626</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.372</t>
+          <t>2026-05-29 09:46:01.384</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779509199397</v>
+        <v>1780022760020</v>
       </c>
       <c r="C68" t="n">
-        <v>87057</v>
+        <v>81418</v>
       </c>
       <c r="D68" t="n">
-        <v>579.1</v>
+        <v>-435.99</v>
       </c>
       <c r="E68" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F68" t="n">
-        <v>644</v>
+        <v>6637</v>
       </c>
       <c r="G68" t="n">
-        <v>270.09</v>
+        <v>264.76</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1362</v>
+      </c>
+      <c r="L68" t="n">
+        <v>111</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.255</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.713</t>
+          <t>2026-05-29 09:46:01.386</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779509199599</v>
+        <v>1780022760220</v>
       </c>
       <c r="C69" t="n">
-        <v>87217</v>
+        <v>81408</v>
       </c>
       <c r="D69" t="n">
-        <v>710.15</v>
+        <v>-424.19</v>
       </c>
       <c r="E69" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F69" t="n">
-        <v>644</v>
+        <v>6637</v>
       </c>
       <c r="G69" t="n">
-        <v>270.09</v>
+        <v>264.76</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L69" t="n">
+        <v>105</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:43.973</t>
+          <t>2026-05-29 09:46:01.388</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779509199800</v>
+        <v>1780022760420</v>
       </c>
       <c r="C70" t="n">
-        <v>87064</v>
+        <v>81475</v>
       </c>
       <c r="D70" t="n">
-        <v>521.64</v>
+        <v>-335.98</v>
       </c>
       <c r="E70" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F70" t="n">
-        <v>644</v>
+        <v>6637</v>
       </c>
       <c r="G70" t="n">
-        <v>270.09</v>
+        <v>264.76</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>967</v>
+      </c>
+      <c r="L70" t="n">
+        <v>111</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.413</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:44.244</t>
+          <t>2026-05-29 09:46:01.740</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779509200001</v>
+        <v>1780022760620</v>
       </c>
       <c r="C71" t="n">
-        <v>87144</v>
+        <v>81425</v>
       </c>
       <c r="D71" t="n">
-        <v>575.5599999999999</v>
+        <v>-369.18</v>
       </c>
       <c r="E71" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F71" t="n">
-        <v>644</v>
+        <v>579</v>
       </c>
       <c r="G71" t="n">
-        <v>270.09</v>
+        <v>266.03</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L71" t="n">
+        <v>112</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:44.245</t>
+          <t>2026-05-29 09:46:01.742</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779509200202</v>
+        <v>1780022760820</v>
       </c>
       <c r="C72" t="n">
-        <v>87224</v>
+        <v>81494</v>
       </c>
       <c r="D72" t="n">
-        <v>626.78</v>
+        <v>-281.72</v>
       </c>
       <c r="E72" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F72" t="n">
-        <v>644</v>
+        <v>280</v>
       </c>
       <c r="G72" t="n">
-        <v>270.09</v>
+        <v>296.72</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>920</v>
+      </c>
+      <c r="L72" t="n">
+        <v>117</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.237</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:44.575</t>
+          <t>2026-05-29 09:46:02.243</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779509200404</v>
+        <v>1780022761021</v>
       </c>
       <c r="C73" t="n">
-        <v>87383</v>
+        <v>81458</v>
       </c>
       <c r="D73" t="n">
-        <v>754.4400000000001</v>
+        <v>-303.63</v>
       </c>
       <c r="E73" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F73" t="n">
-        <v>1469</v>
+        <v>280</v>
       </c>
       <c r="G73" t="n">
-        <v>350.85</v>
+        <v>296.72</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L73" t="n">
+        <v>106</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:44.832</t>
+          <t>2026-05-29 09:46:02.245</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779509200605</v>
+        <v>1780022761220</v>
       </c>
       <c r="C74" t="n">
-        <v>87095</v>
+        <v>81851</v>
       </c>
       <c r="D74" t="n">
-        <v>428.72</v>
+        <v>104.55</v>
       </c>
       <c r="E74" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F74" t="n">
-        <v>1469</v>
+        <v>280</v>
       </c>
       <c r="G74" t="n">
-        <v>350.85</v>
+        <v>296.72</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L74" t="n">
+        <v>124</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.295</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.145</t>
+          <t>2026-05-29 09:46:02.263</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779509200806</v>
+        <v>1780022761420</v>
       </c>
       <c r="C75" t="n">
-        <v>87303</v>
+        <v>82580</v>
       </c>
       <c r="D75" t="n">
-        <v>615.28</v>
+        <v>828.3200000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F75" t="n">
-        <v>1469</v>
+        <v>280</v>
       </c>
       <c r="G75" t="n">
-        <v>350.85</v>
+        <v>296.72</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>843</v>
+      </c>
+      <c r="L75" t="n">
+        <v>107</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.843</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.147</t>
+          <t>2026-05-29 09:46:02.729</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779509201008</v>
+        <v>1780022761620</v>
       </c>
       <c r="C76" t="n">
-        <v>87473</v>
+        <v>83363</v>
       </c>
       <c r="D76" t="n">
-        <v>754.52</v>
+        <v>1569.9</v>
       </c>
       <c r="E76" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="F76" t="n">
-        <v>584</v>
+        <v>280</v>
       </c>
       <c r="G76" t="n">
-        <v>279.45</v>
+        <v>296.72</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L76" t="n">
+        <v>121</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.603</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.389</t>
+          <t>2026-05-29 09:46:02.731</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779509201209</v>
+        <v>1780022761839</v>
       </c>
       <c r="C77" t="n">
-        <v>87079</v>
+        <v>83908</v>
       </c>
       <c r="D77" t="n">
-        <v>322.79</v>
+        <v>2036.41</v>
       </c>
       <c r="E77" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="F77" t="n">
-        <v>584</v>
+        <v>280</v>
       </c>
       <c r="G77" t="n">
-        <v>279.45</v>
+        <v>296.72</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>891</v>
+      </c>
+      <c r="L77" t="n">
+        <v>106</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.677</t>
+          <t>2026-05-29 09:46:04.006</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779509201410</v>
+        <v>1780022762039</v>
       </c>
       <c r="C78" t="n">
-        <v>87218</v>
+        <v>83365</v>
       </c>
       <c r="D78" t="n">
-        <v>445.65</v>
+        <v>1391.59</v>
       </c>
       <c r="E78" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="F78" t="n">
-        <v>584</v>
+        <v>280</v>
       </c>
       <c r="G78" t="n">
-        <v>279.45</v>
+        <v>296.72</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1965</v>
+      </c>
+      <c r="L78" t="n">
+        <v>123</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.844</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.970</t>
+          <t>2026-05-29 09:46:04.008</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779509201612</v>
+        <v>1780022762239</v>
       </c>
       <c r="C79" t="n">
-        <v>87458</v>
+        <v>83313</v>
       </c>
       <c r="D79" t="n">
-        <v>663.37</v>
+        <v>1270.01</v>
       </c>
       <c r="E79" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="F79" t="n">
-        <v>584</v>
+        <v>280</v>
       </c>
       <c r="G79" t="n">
-        <v>279.45</v>
+        <v>296.72</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1768</v>
+      </c>
+      <c r="L79" t="n">
+        <v>106</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.516</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:45.971</t>
+          <t>2026-05-29 09:46:04.282</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779509201813</v>
+        <v>1780022762439</v>
       </c>
       <c r="C80" t="n">
-        <v>87256</v>
+        <v>82923</v>
       </c>
       <c r="D80" t="n">
-        <v>428.2</v>
+        <v>816.51</v>
       </c>
       <c r="E80" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F80" t="n">
-        <v>725</v>
+        <v>280</v>
       </c>
       <c r="G80" t="n">
-        <v>279.09</v>
+        <v>296.72</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1841</v>
+      </c>
+      <c r="L80" t="n">
+        <v>120</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.862</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:46.221</t>
+          <t>2026-05-29 09:46:04.284</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779509202014</v>
+        <v>1780022762639</v>
       </c>
       <c r="C81" t="n">
-        <v>87171</v>
+        <v>82756</v>
       </c>
       <c r="D81" t="n">
-        <v>321.79</v>
+        <v>608.6799999999999</v>
       </c>
       <c r="E81" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F81" t="n">
-        <v>725</v>
+        <v>280</v>
       </c>
       <c r="G81" t="n">
-        <v>279.09</v>
+        <v>296.72</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1644</v>
+      </c>
+      <c r="L81" t="n">
+        <v>107</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.381</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:46.225</t>
+          <t>2026-05-29 09:46:04.285</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779509202215</v>
+        <v>1780022762839</v>
       </c>
       <c r="C82" t="n">
-        <v>87307</v>
+        <v>83236</v>
       </c>
       <c r="D82" t="n">
-        <v>441.7</v>
+        <v>1058.25</v>
       </c>
       <c r="E82" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F82" t="n">
-        <v>725</v>
+        <v>280</v>
       </c>
       <c r="G82" t="n">
-        <v>279.09</v>
+        <v>296.72</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1445</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.162</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:46.458</t>
+          <t>2026-05-29 09:46:04.287</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779509202417</v>
+        <v>1780022763039</v>
       </c>
       <c r="C83" t="n">
-        <v>87451</v>
+        <v>83283</v>
       </c>
       <c r="D83" t="n">
-        <v>563.62</v>
+        <v>1052.34</v>
       </c>
       <c r="E83" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F83" t="n">
-        <v>724</v>
+        <v>280</v>
       </c>
       <c r="G83" t="n">
-        <v>278.19</v>
+        <v>296.72</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1247</v>
+      </c>
+      <c r="L83" t="n">
+        <v>108</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.092</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:46.801</t>
+          <t>2026-05-29 09:46:04.289</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779509202618</v>
+        <v>1780022763239</v>
       </c>
       <c r="C84" t="n">
-        <v>87091</v>
+        <v>83319</v>
       </c>
       <c r="D84" t="n">
-        <v>175.44</v>
+        <v>1035.72</v>
       </c>
       <c r="E84" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F84" t="n">
-        <v>724</v>
+        <v>280</v>
       </c>
       <c r="G84" t="n">
-        <v>278.19</v>
+        <v>296.72</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1048</v>
+      </c>
+      <c r="L84" t="n">
+        <v>107</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.519</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:47.096</t>
+          <t>2026-05-29 09:46:04.291</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779509202819</v>
+        <v>1780022763439</v>
       </c>
       <c r="C85" t="n">
-        <v>87216</v>
+        <v>82662</v>
       </c>
       <c r="D85" t="n">
-        <v>291.66</v>
+        <v>326.93</v>
       </c>
       <c r="E85" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F85" t="n">
-        <v>724</v>
+        <v>280</v>
       </c>
       <c r="G85" t="n">
-        <v>278.19</v>
+        <v>296.72</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J85" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K85" t="n">
+        <v>850</v>
+      </c>
+      <c r="L85" t="n">
+        <v>119</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.761</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:47.348</t>
+          <t>2026-05-29 09:46:04.853</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779509203021</v>
+        <v>1780022763658</v>
       </c>
       <c r="C86" t="n">
-        <v>87396</v>
+        <v>82278</v>
       </c>
       <c r="D86" t="n">
-        <v>457.08</v>
+        <v>-73.41</v>
       </c>
       <c r="E86" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F86" t="n">
-        <v>724</v>
+        <v>280</v>
       </c>
       <c r="G86" t="n">
-        <v>278.19</v>
+        <v>296.72</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1194</v>
+      </c>
+      <c r="L86" t="n">
+        <v>110</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:47.351</t>
+          <t>2026-05-29 09:46:04.855</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779509203222</v>
+        <v>1780022763858</v>
       </c>
       <c r="C87" t="n">
-        <v>87560</v>
+        <v>82682</v>
       </c>
       <c r="D87" t="n">
-        <v>598.23</v>
+        <v>334.26</v>
       </c>
       <c r="E87" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F87" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G87" t="n">
-        <v>276.35</v>
+        <v>296.72</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>996</v>
+      </c>
+      <c r="L87" t="n">
+        <v>107</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:47.639</t>
+          <t>2026-05-29 09:46:05.152</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779509203423</v>
+        <v>1780022764058</v>
       </c>
       <c r="C88" t="n">
-        <v>87151</v>
+        <v>81390</v>
       </c>
       <c r="D88" t="n">
-        <v>159.32</v>
+        <v>-974.46</v>
       </c>
       <c r="E88" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F88" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G88" t="n">
-        <v>276.35</v>
+        <v>296.72</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L88" t="n">
+        <v>118</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.744</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:47.917</t>
+          <t>2026-05-29 09:46:05.167</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779509203624</v>
+        <v>1780022764258</v>
       </c>
       <c r="C89" t="n">
-        <v>87281</v>
+        <v>78116</v>
       </c>
       <c r="D89" t="n">
-        <v>281.35</v>
+        <v>-4199.73</v>
       </c>
       <c r="E89" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F89" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G89" t="n">
-        <v>276.35</v>
+        <v>296.72</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>908</v>
+      </c>
+      <c r="L89" t="n">
+        <v>116</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.125</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:48.445</t>
+          <t>2026-05-29 09:46:05.737</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779509203826</v>
+        <v>1780022764458</v>
       </c>
       <c r="C90" t="n">
-        <v>87486</v>
+        <v>76894</v>
       </c>
       <c r="D90" t="n">
-        <v>472.28</v>
+        <v>-5211.75</v>
       </c>
       <c r="E90" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F90" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G90" t="n">
-        <v>276.35</v>
+        <v>296.72</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1278</v>
+      </c>
+      <c r="L90" t="n">
+        <v>116</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:48.747</t>
+          <t>2026-05-29 09:46:05.739</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779509204027</v>
+        <v>1780022764658</v>
       </c>
       <c r="C91" t="n">
-        <v>87205</v>
+        <v>77161</v>
       </c>
       <c r="D91" t="n">
-        <v>167.67</v>
+        <v>-4684.16</v>
       </c>
       <c r="E91" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F91" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G91" t="n">
-        <v>269.03</v>
+        <v>296.72</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L91" t="n">
+        <v>110</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.608</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:48.776</t>
+          <t>2026-05-29 09:46:06.073</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779509204228</v>
+        <v>1780022764858</v>
       </c>
       <c r="C92" t="n">
-        <v>87284</v>
+        <v>76985</v>
       </c>
       <c r="D92" t="n">
-        <v>238.29</v>
+        <v>-4625.95</v>
       </c>
       <c r="E92" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F92" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G92" t="n">
-        <v>269.03</v>
+        <v>296.72</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L92" t="n">
+        <v>113</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.976</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:48.779</t>
+          <t>2026-05-29 09:46:06.074</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779509204430</v>
+        <v>1780022765058</v>
       </c>
       <c r="C93" t="n">
-        <v>87344</v>
+        <v>76928</v>
       </c>
       <c r="D93" t="n">
-        <v>286.37</v>
+        <v>-4451.65</v>
       </c>
       <c r="E93" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F93" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G93" t="n">
-        <v>269.03</v>
+        <v>296.72</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1015</v>
+      </c>
+      <c r="L93" t="n">
+        <v>117</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.867</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:49.089</t>
+          <t>2026-05-29 09:46:06.416</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779509204631</v>
+        <v>1780022765277</v>
       </c>
       <c r="C94" t="n">
-        <v>87451</v>
+        <v>76813</v>
       </c>
       <c r="D94" t="n">
-        <v>379.05</v>
+        <v>-4344.07</v>
       </c>
       <c r="E94" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F94" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G94" t="n">
-        <v>258.04</v>
+        <v>296.72</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1138</v>
+      </c>
+      <c r="L94" t="n">
+        <v>110</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:49.350</t>
+          <t>2026-05-29 09:46:06.469</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779509204832</v>
+        <v>1780022765477</v>
       </c>
       <c r="C95" t="n">
-        <v>87192</v>
+        <v>76726</v>
       </c>
       <c r="D95" t="n">
-        <v>101.1</v>
+        <v>-4213.87</v>
       </c>
       <c r="E95" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F95" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G95" t="n">
-        <v>258.04</v>
+        <v>296.72</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>990</v>
+      </c>
+      <c r="L95" t="n">
+        <v>115</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.426</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:49.351</t>
+          <t>2026-05-29 09:46:06.760</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779509205034</v>
+        <v>1780022765677</v>
       </c>
       <c r="C96" t="n">
-        <v>87380</v>
+        <v>76477</v>
       </c>
       <c r="D96" t="n">
-        <v>284.04</v>
+        <v>-4252.17</v>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F96" t="n">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="G96" t="n">
-        <v>258.04</v>
+        <v>296.72</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L96" t="n">
+        <v>117</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.618</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:49.352</t>
+          <t>2026-05-29 09:46:06.770</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779509205235</v>
+        <v>1780022765877</v>
       </c>
       <c r="C97" t="n">
-        <v>87538</v>
+        <v>76457</v>
       </c>
       <c r="D97" t="n">
-        <v>427.84</v>
+        <v>-4059.56</v>
       </c>
       <c r="E97" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F97" t="n">
-        <v>543</v>
+        <v>280</v>
       </c>
       <c r="G97" t="n">
-        <v>265.53</v>
+        <v>296.72</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>892</v>
+      </c>
+      <c r="L97" t="n">
+        <v>112</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:49.896</t>
+          <t>2026-05-29 09:46:07.507</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779509205436</v>
+        <v>1780022766077</v>
       </c>
       <c r="C98" t="n">
-        <v>87235</v>
+        <v>76652</v>
       </c>
       <c r="D98" t="n">
-        <v>103.45</v>
+        <v>-3661.59</v>
       </c>
       <c r="E98" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F98" t="n">
-        <v>543</v>
+        <v>280</v>
       </c>
       <c r="G98" t="n">
-        <v>265.53</v>
+        <v>296.72</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L98" t="n">
+        <v>107</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.528</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:50.183</t>
+          <t>2026-05-29 09:46:07.508</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779509205637</v>
+        <v>1780022766277</v>
       </c>
       <c r="C99" t="n">
-        <v>87312</v>
+        <v>76573</v>
       </c>
       <c r="D99" t="n">
-        <v>175.28</v>
+        <v>-3557.51</v>
       </c>
       <c r="E99" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F99" t="n">
-        <v>543</v>
+        <v>280</v>
       </c>
       <c r="G99" t="n">
-        <v>265.53</v>
+        <v>296.72</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1230</v>
+      </c>
+      <c r="L99" t="n">
+        <v>124</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.556</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:50.190</t>
+          <t>2026-05-29 09:46:07.989</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779509205839</v>
+        <v>1780022766478</v>
       </c>
       <c r="C100" t="n">
-        <v>87492</v>
+        <v>76501</v>
       </c>
       <c r="D100" t="n">
-        <v>346.51</v>
+        <v>-3451.63</v>
       </c>
       <c r="E100" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F100" t="n">
-        <v>543</v>
+        <v>5537</v>
       </c>
       <c r="G100" t="n">
-        <v>265.53</v>
+        <v>296.72</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1510</v>
+      </c>
+      <c r="L100" t="n">
+        <v>111</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:50.190</t>
+          <t>2026-05-29 09:46:07.990</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779509206040</v>
+        <v>1780022766677</v>
       </c>
       <c r="C101" t="n">
-        <v>87162</v>
+        <v>76553</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3227.05</v>
       </c>
       <c r="E101" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>5537</v>
       </c>
       <c r="G101" t="n">
-        <v>257.58</v>
+        <v>296.72</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1312</v>
+      </c>
+      <c r="L101" t="n">
+        <v>120</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:50.426</t>
+          <t>2026-05-29 09:46:07.991</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779509206241</v>
+        <v>1780022766877</v>
       </c>
       <c r="C102" t="n">
-        <v>87168</v>
+        <v>76428</v>
       </c>
       <c r="D102" t="n">
-        <v>5.23</v>
+        <v>-3190.7</v>
       </c>
       <c r="E102" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F102" t="n">
-        <v>745</v>
+        <v>5537</v>
       </c>
       <c r="G102" t="n">
-        <v>257.58</v>
+        <v>296.72</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L102" t="n">
+        <v>111</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:50.426</t>
+          <t>2026-05-29 09:46:08.678</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779509206443</v>
+        <v>1780022767097</v>
       </c>
       <c r="C103" t="n">
-        <v>87305</v>
+        <v>76039</v>
       </c>
       <c r="D103" t="n">
-        <v>141.97</v>
+        <v>-3420.16</v>
       </c>
       <c r="E103" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F103" t="n">
-        <v>745</v>
+        <v>5537</v>
       </c>
       <c r="G103" t="n">
-        <v>257.58</v>
+        <v>296.72</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1580</v>
+      </c>
+      <c r="L103" t="n">
+        <v>110</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:51.011</t>
+          <t>2026-05-29 09:46:08.680</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779509206644</v>
+        <v>1780022767296</v>
       </c>
       <c r="C104" t="n">
-        <v>87174</v>
+        <v>76230</v>
       </c>
       <c r="D104" t="n">
-        <v>3.87</v>
+        <v>-3058.15</v>
       </c>
       <c r="E104" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F104" t="n">
-        <v>725</v>
+        <v>5537</v>
       </c>
       <c r="G104" t="n">
-        <v>254.55</v>
+        <v>296.72</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1383</v>
+      </c>
+      <c r="L104" t="n">
+        <v>122</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.537</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:51.287</t>
+          <t>2026-05-29 09:46:08.680</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779509206845</v>
+        <v>1780022767496</v>
       </c>
       <c r="C105" t="n">
-        <v>87016</v>
+        <v>76024</v>
       </c>
       <c r="D105" t="n">
-        <v>-154.32</v>
+        <v>-3111.25</v>
       </c>
       <c r="E105" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F105" t="n">
-        <v>725</v>
+        <v>5537</v>
       </c>
       <c r="G105" t="n">
-        <v>254.55</v>
+        <v>296.72</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1184</v>
+      </c>
+      <c r="L105" t="n">
+        <v>119</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:51.288</t>
+          <t>2026-05-29 09:46:09.302</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779509207046</v>
+        <v>1780022767697</v>
       </c>
       <c r="C106" t="n">
-        <v>87165</v>
+        <v>76013</v>
       </c>
       <c r="D106" t="n">
-        <v>2.39</v>
+        <v>-2966.68</v>
       </c>
       <c r="E106" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F106" t="n">
-        <v>725</v>
+        <v>5537</v>
       </c>
       <c r="G106" t="n">
-        <v>254.55</v>
+        <v>296.72</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L106" t="n">
+        <v>111</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.454</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:51.738</t>
+          <t>2026-05-29 09:46:09.339</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779509207248</v>
+        <v>1780022767916</v>
       </c>
       <c r="C107" t="n">
-        <v>87180</v>
+        <v>76218</v>
       </c>
       <c r="D107" t="n">
-        <v>17.27</v>
+        <v>-2613.35</v>
       </c>
       <c r="E107" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F107" t="n">
-        <v>644</v>
+        <v>5537</v>
       </c>
       <c r="G107" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1422</v>
+      </c>
+      <c r="L107" t="n">
+        <v>121</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.071</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.028</t>
+          <t>2026-05-29 09:46:09.341</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779509207449</v>
+        <v>1780022768116</v>
       </c>
       <c r="C108" t="n">
-        <v>86933</v>
+        <v>76041</v>
       </c>
       <c r="D108" t="n">
-        <v>-230.59</v>
+        <v>-2659.68</v>
       </c>
       <c r="E108" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F108" t="n">
-        <v>644</v>
+        <v>1659</v>
       </c>
       <c r="G108" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L108" t="n">
+        <v>111</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.145</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.049</t>
+          <t>2026-05-29 09:46:09.343</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779509207650</v>
+        <v>1780022768316</v>
       </c>
       <c r="C109" t="n">
-        <v>87099</v>
+        <v>75951</v>
       </c>
       <c r="D109" t="n">
-        <v>-53.06</v>
+        <v>-2616.7</v>
       </c>
       <c r="E109" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F109" t="n">
-        <v>644</v>
+        <v>1659</v>
       </c>
       <c r="G109" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1026</v>
+      </c>
+      <c r="L109" t="n">
+        <v>119</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.167</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.082</t>
+          <t>2026-05-29 09:46:10.006</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779509207852</v>
+        <v>1780022768516</v>
       </c>
       <c r="C110" t="n">
-        <v>87195</v>
+        <v>75753</v>
       </c>
       <c r="D110" t="n">
-        <v>45.59</v>
+        <v>-2683.86</v>
       </c>
       <c r="E110" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F110" t="n">
-        <v>584</v>
+        <v>1659</v>
       </c>
       <c r="G110" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1489</v>
+      </c>
+      <c r="L110" t="n">
+        <v>113</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.977</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.465</t>
+          <t>2026-05-29 09:46:10.007</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779509208053</v>
+        <v>1780022768735</v>
       </c>
       <c r="C111" t="n">
-        <v>86789</v>
+        <v>75580</v>
       </c>
       <c r="D111" t="n">
-        <v>-362.69</v>
+        <v>-2722.67</v>
       </c>
       <c r="E111" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F111" t="n">
-        <v>584</v>
+        <v>1659</v>
       </c>
       <c r="G111" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J111" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1271</v>
+      </c>
+      <c r="L111" t="n">
+        <v>116</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.738</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.795</t>
+          <t>2026-05-29 09:46:10.527</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779509208254</v>
+        <v>1780022768936</v>
       </c>
       <c r="C112" t="n">
-        <v>86959</v>
+        <v>75611</v>
       </c>
       <c r="D112" t="n">
-        <v>-174.55</v>
+        <v>-2555.54</v>
       </c>
       <c r="E112" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F112" t="n">
-        <v>584</v>
+        <v>1659</v>
       </c>
       <c r="G112" t="n">
-        <v>74.98</v>
+        <v>296.72</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1591</v>
+      </c>
+      <c r="L112" t="n">
+        <v>110</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:52.801</t>
+          <t>2026-05-29 09:46:10.538</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779509208456</v>
+        <v>1780022769135</v>
       </c>
       <c r="C113" t="n">
-        <v>87149</v>
+        <v>75570</v>
       </c>
       <c r="D113" t="n">
-        <v>24.17</v>
+        <v>-2468.76</v>
       </c>
       <c r="E113" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F113" t="n">
-        <v>624</v>
+        <v>1659</v>
       </c>
       <c r="G113" t="n">
-        <v>76.90000000000001</v>
+        <v>296.72</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1403</v>
+      </c>
+      <c r="L113" t="n">
+        <v>122</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:53.075</t>
+          <t>2026-05-29 09:46:11.046</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779509208657</v>
+        <v>1780022769336</v>
       </c>
       <c r="C114" t="n">
-        <v>86757</v>
+        <v>75509</v>
       </c>
       <c r="D114" t="n">
-        <v>-369.03</v>
+        <v>-2406.32</v>
       </c>
       <c r="E114" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F114" t="n">
-        <v>624</v>
+        <v>1659</v>
       </c>
       <c r="G114" t="n">
-        <v>76.90000000000001</v>
+        <v>296.72</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1709</v>
+      </c>
+      <c r="L114" t="n">
+        <v>111</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:53.373</t>
+          <t>2026-05-29 09:46:11.048</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779509208858</v>
+        <v>1780022769535</v>
       </c>
       <c r="C115" t="n">
-        <v>86872</v>
+        <v>75381</v>
       </c>
       <c r="D115" t="n">
-        <v>-235.58</v>
+        <v>-2414.01</v>
       </c>
       <c r="E115" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F115" t="n">
-        <v>624</v>
+        <v>1659</v>
       </c>
       <c r="G115" t="n">
-        <v>76.90000000000001</v>
+        <v>296.72</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1512</v>
+      </c>
+      <c r="L115" t="n">
+        <v>112</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.121</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:53.374</t>
+          <t>2026-05-29 09:46:11.049</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779509209059</v>
+        <v>1780022769735</v>
       </c>
       <c r="C116" t="n">
-        <v>87036</v>
+        <v>75473</v>
       </c>
       <c r="D116" t="n">
-        <v>-59.8</v>
+        <v>-2201.31</v>
       </c>
       <c r="E116" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F116" t="n">
-        <v>624</v>
+        <v>1659</v>
       </c>
       <c r="G116" t="n">
-        <v>76.90000000000001</v>
+        <v>296.72</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1313</v>
+      </c>
+      <c r="L116" t="n">
+        <v>116</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:53.620</t>
+          <t>2026-05-29 09:46:11.050</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779509209261</v>
+        <v>1780022769935</v>
       </c>
       <c r="C117" t="n">
-        <v>86694</v>
+        <v>75533</v>
       </c>
       <c r="D117" t="n">
-        <v>-398.81</v>
+        <v>-2031.24</v>
       </c>
       <c r="E117" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F117" t="n">
-        <v>664</v>
+        <v>1659</v>
       </c>
       <c r="G117" t="n">
-        <v>75.62</v>
+        <v>296.72</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L117" t="n">
+        <v>103</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:53.642</t>
+          <t>2026-05-29 09:46:12.271</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779509209462</v>
+        <v>1780022770135</v>
       </c>
       <c r="C118" t="n">
-        <v>86803</v>
+        <v>75457</v>
       </c>
       <c r="D118" t="n">
-        <v>-269.87</v>
+        <v>-2005.68</v>
       </c>
       <c r="E118" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F118" t="n">
-        <v>664</v>
+        <v>2119</v>
       </c>
       <c r="G118" t="n">
-        <v>75.62</v>
+        <v>296.72</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2135</v>
+      </c>
+      <c r="L118" t="n">
+        <v>115</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:54.019</t>
+          <t>2026-05-29 09:46:12.283</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779509209663</v>
+        <v>1780022770354</v>
       </c>
       <c r="C119" t="n">
-        <v>87042</v>
+        <v>75408</v>
       </c>
       <c r="D119" t="n">
-        <v>-17.38</v>
+        <v>-1954.39</v>
       </c>
       <c r="E119" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F119" t="n">
-        <v>664</v>
+        <v>2119</v>
       </c>
       <c r="G119" t="n">
-        <v>75.62</v>
+        <v>296.72</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1927</v>
+      </c>
+      <c r="L119" t="n">
+        <v>120</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.788</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:54.317</t>
+          <t>2026-05-29 09:46:12.285</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779509209865</v>
+        <v>1780022770554</v>
       </c>
       <c r="C120" t="n">
-        <v>86882</v>
+        <v>75483</v>
       </c>
       <c r="D120" t="n">
-        <v>-176.51</v>
+        <v>-1781.67</v>
       </c>
       <c r="E120" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F120" t="n">
-        <v>604</v>
+        <v>2119</v>
       </c>
       <c r="G120" t="n">
-        <v>74.55</v>
+        <v>296.72</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1729</v>
+      </c>
+      <c r="L120" t="n">
+        <v>111</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.763</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:12.287</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022770754</v>
+      </c>
+      <c r="C121" t="n">
+        <v>75339</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-1836.59</v>
+      </c>
+      <c r="E121" t="n">
+        <v>114</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G121" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1531</v>
+      </c>
+      <c r="L121" t="n">
+        <v>104</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.266</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:12.785</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022770954</v>
+      </c>
+      <c r="C122" t="n">
+        <v>75251</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-1832.76</v>
+      </c>
+      <c r="E122" t="n">
+        <v>114</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G122" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1830</v>
+      </c>
+      <c r="L122" t="n">
+        <v>126</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:12.786</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022771154</v>
+      </c>
+      <c r="C123" t="n">
+        <v>75455</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-1537.12</v>
+      </c>
+      <c r="E123" t="n">
+        <v>114</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G123" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1631</v>
+      </c>
+      <c r="L123" t="n">
+        <v>112</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:12.787</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022771354</v>
+      </c>
+      <c r="C124" t="n">
+        <v>75394</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-1521.27</v>
+      </c>
+      <c r="E124" t="n">
+        <v>106</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G124" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1432</v>
+      </c>
+      <c r="L124" t="n">
+        <v>112</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.863</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:12.788</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022771554</v>
+      </c>
+      <c r="C125" t="n">
+        <v>75347</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1492.2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>106</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G125" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1233</v>
+      </c>
+      <c r="L125" t="n">
+        <v>119</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:13.441</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022771754</v>
+      </c>
+      <c r="C126" t="n">
+        <v>75299</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1465.59</v>
+      </c>
+      <c r="E126" t="n">
+        <v>106</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G126" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1685</v>
+      </c>
+      <c r="L126" t="n">
+        <v>116</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.104</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:13.633</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022771973</v>
+      </c>
+      <c r="C127" t="n">
+        <v>75306</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-1385.31</v>
+      </c>
+      <c r="E127" t="n">
+        <v>106</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G127" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J127" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1658</v>
+      </c>
+      <c r="L127" t="n">
+        <v>120</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.663</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:13.634</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022772173</v>
+      </c>
+      <c r="C128" t="n">
+        <v>75297</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-1325.05</v>
+      </c>
+      <c r="E128" t="n">
+        <v>106</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G128" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1460</v>
+      </c>
+      <c r="L128" t="n">
+        <v>126</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.093</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:13.636</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022772373</v>
+      </c>
+      <c r="C129" t="n">
+        <v>75540</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-1015.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>106</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G129" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1262</v>
+      </c>
+      <c r="L129" t="n">
+        <v>111</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.095</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:13.637</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022772573</v>
+      </c>
+      <c r="C130" t="n">
+        <v>75534</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-971.01</v>
+      </c>
+      <c r="E130" t="n">
+        <v>104</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G130" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L130" t="n">
+        <v>111</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.049</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022772773</v>
+      </c>
+      <c r="C131" t="n">
+        <v>75507</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-949.46</v>
+      </c>
+      <c r="E131" t="n">
+        <v>104</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G131" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1274</v>
+      </c>
+      <c r="L131" t="n">
+        <v>112</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.801</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.051</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022772973</v>
+      </c>
+      <c r="C132" t="n">
+        <v>75446</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-962.98</v>
+      </c>
+      <c r="E132" t="n">
+        <v>104</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G132" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J132" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L132" t="n">
+        <v>125</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.293</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.053</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022773173</v>
+      </c>
+      <c r="C133" t="n">
+        <v>75455</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-905.83</v>
+      </c>
+      <c r="E133" t="n">
+        <v>104</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G133" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>878</v>
+      </c>
+      <c r="L133" t="n">
+        <v>127</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.464</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.444</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022773373</v>
+      </c>
+      <c r="C134" t="n">
+        <v>75345</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-970.54</v>
+      </c>
+      <c r="E134" t="n">
+        <v>104</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G134" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1069</v>
+      </c>
+      <c r="L134" t="n">
+        <v>122</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.768</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.784</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022773593</v>
+      </c>
+      <c r="C135" t="n">
+        <v>75127</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-1140.02</v>
+      </c>
+      <c r="E135" t="n">
+        <v>104</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G135" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L135" t="n">
+        <v>112</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.785</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022773792</v>
+      </c>
+      <c r="C136" t="n">
+        <v>75325</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-885.01</v>
+      </c>
+      <c r="E136" t="n">
+        <v>104</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G136" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>992</v>
+      </c>
+      <c r="L136" t="n">
+        <v>128</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.652</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:14.786</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022773992</v>
+      </c>
+      <c r="C137" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-853.76</v>
+      </c>
+      <c r="E137" t="n">
+        <v>104</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1539</v>
+      </c>
+      <c r="G137" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>793</v>
+      </c>
+      <c r="L137" t="n">
+        <v>112</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:15.582</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022774192</v>
+      </c>
+      <c r="C138" t="n">
+        <v>75317</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-806.08</v>
+      </c>
+      <c r="E138" t="n">
+        <v>104</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1539</v>
+      </c>
+      <c r="G138" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1389</v>
+      </c>
+      <c r="L138" t="n">
+        <v>125</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:15.583</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022774392</v>
+      </c>
+      <c r="C139" t="n">
+        <v>75315</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-767.77</v>
+      </c>
+      <c r="E139" t="n">
+        <v>104</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1539</v>
+      </c>
+      <c r="G139" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L139" t="n">
+        <v>113</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.101</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:17.425</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022774592</v>
+      </c>
+      <c r="C140" t="n">
+        <v>75323</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-721.38</v>
+      </c>
+      <c r="E140" t="n">
+        <v>103</v>
+      </c>
+      <c r="F140" t="n">
+        <v>600</v>
+      </c>
+      <c r="G140" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2832</v>
+      </c>
+      <c r="L140" t="n">
+        <v>113</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.466</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:17.446</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022774792</v>
+      </c>
+      <c r="C141" t="n">
+        <v>75154</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-854.3099999999999</v>
+      </c>
+      <c r="E141" t="n">
+        <v>103</v>
+      </c>
+      <c r="F141" t="n">
+        <v>600</v>
+      </c>
+      <c r="G141" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2653</v>
+      </c>
+      <c r="L141" t="n">
+        <v>108</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:17.458</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022774992</v>
+      </c>
+      <c r="C142" t="n">
+        <v>75009</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-956.6</v>
+      </c>
+      <c r="E142" t="n">
+        <v>103</v>
+      </c>
+      <c r="F142" t="n">
+        <v>600</v>
+      </c>
+      <c r="G142" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2465</v>
+      </c>
+      <c r="L142" t="n">
+        <v>114</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.513</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:17.458</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022775211</v>
+      </c>
+      <c r="C143" t="n">
+        <v>75027</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-890.77</v>
+      </c>
+      <c r="E143" t="n">
+        <v>103</v>
+      </c>
+      <c r="F143" t="n">
+        <v>600</v>
+      </c>
+      <c r="G143" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2247</v>
+      </c>
+      <c r="L143" t="n">
+        <v>106</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:46:18.082</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022775411</v>
+      </c>
+      <c r="C144" t="n">
+        <v>75049</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-824.23</v>
+      </c>
+      <c r="E144" t="n">
+        <v>103</v>
+      </c>
+      <c r="F144" t="n">
+        <v>600</v>
+      </c>
+      <c r="G144" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2669</v>
+      </c>
+      <c r="L144" t="n">
+        <v>111</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.359</v>
       </c>
     </row>
   </sheetData>
